--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="124">
   <si>
     <t>Result</t>
   </si>
@@ -367,6 +367,48 @@
   </si>
   <si>
     <t>Thu Jul 09 17:07:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:30:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:32:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:32:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:33:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:33:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:34:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:35:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:36:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:37:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:37:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:38:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 01:39:04 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1031,7 @@
         <v>50</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
@@ -1030,7 +1072,7 @@
         <v>50</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>36</v>
@@ -1071,7 +1113,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>47</v>
@@ -1112,7 +1154,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>48</v>
@@ -1296,7 +1338,7 @@
         <v>50</v>
       </c>
       <c r="B2" t="s" s="6">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1343,7 +1385,7 @@
         <v>50</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>33</v>
@@ -1414,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s" s="6">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>34</v>
@@ -1455,7 +1497,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="s" s="6">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>35</v>
@@ -1497,7 +1539,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s" s="6">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>49</v>
